--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99413</v>
+        <v>99426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99426</v>
+        <v>99428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99428</v>
+        <v>99431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99431</v>
+        <v>99441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99441</v>
+        <v>99442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99442</v>
+        <v>99447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99447</v>
+        <v>99449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99449</v>
+        <v>99455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99455</v>
+        <v>99467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99467</v>
+        <v>99468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99468</v>
+        <v>99471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40153-2025 artfynd.xlsx
+++ b/artfynd/A 40153-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137156421</v>
       </c>
       <c r="B2" t="n">
-        <v>99471</v>
+        <v>99475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
